--- a/silver_to_gold_validation.xlsx
+++ b/silver_to_gold_validation.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uthej\Downloads\PEI_assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF18038-8BB1-4387-A552-A8870A608CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5032EA-7EDB-4EBD-8064-F8FF99598F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{BC5507A9-D27E-444C-93EA-C153FA16561C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{BC5507A9-D27E-444C-93EA-C153FA16561C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Business Requirement" sheetId="8" r:id="rId1"/>
+    <sheet name="Business Requirements" sheetId="8" r:id="rId1"/>
     <sheet name="schema map silver to gold" sheetId="1" r:id="rId2"/>
     <sheet name="todo" sheetId="2" r:id="rId3"/>
-    <sheet name="test cases" sheetId="3" r:id="rId4"/>
-    <sheet name="REQ1_test_execution" sheetId="4" r:id="rId5"/>
-    <sheet name="REQ1_test_final_results" sheetId="6" r:id="rId6"/>
-    <sheet name="REQ1_gap" sheetId="9" r:id="rId7"/>
-    <sheet name="REQ2_test_execution" sheetId="7" r:id="rId8"/>
-    <sheet name="REQ2_test_final_results" sheetId="10" r:id="rId9"/>
-    <sheet name="REQ3_test_execution" sheetId="12" r:id="rId10"/>
-    <sheet name="REQ3_test_final_results" sheetId="13" r:id="rId11"/>
-    <sheet name="REQ4_test_execution" sheetId="14" r:id="rId12"/>
-    <sheet name="REQ4_test_final_results" sheetId="15" r:id="rId13"/>
-    <sheet name="REQ5_test_execution" sheetId="16" r:id="rId14"/>
-    <sheet name="REQ5_test_final_results" sheetId="17" r:id="rId15"/>
+    <sheet name="REQ1_gap" sheetId="9" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="18" r:id="rId5"/>
+    <sheet name="test cases" sheetId="3" r:id="rId6"/>
+    <sheet name="REQ1_test_execution" sheetId="4" r:id="rId7"/>
+    <sheet name="REQ1_test_final_results" sheetId="6" r:id="rId8"/>
+    <sheet name="REQ2_test_execution" sheetId="7" r:id="rId9"/>
+    <sheet name="REQ2_test_final_results" sheetId="10" r:id="rId10"/>
+    <sheet name="REQ3_test_execution" sheetId="12" r:id="rId11"/>
+    <sheet name="REQ3_test_final_results" sheetId="13" r:id="rId12"/>
+    <sheet name="REQ4_test_execution" sheetId="14" r:id="rId13"/>
+    <sheet name="REQ4_test_final_results" sheetId="15" r:id="rId14"/>
+    <sheet name="REQ5_test_execution" sheetId="16" r:id="rId15"/>
+    <sheet name="REQ5_test_final_results" sheetId="17" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1882" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="430">
   <si>
     <t>Source_Table</t>
   </si>
@@ -704,9 +705,6 @@
     <t>Requirement ID</t>
   </si>
   <si>
-    <t>Shipping is at customer level, not order level</t>
-  </si>
-  <si>
     <t>Requirement Gap</t>
   </si>
   <si>
@@ -715,11 +713,6 @@
   <si>
     <t>Confirm if delivered orders should be excluded
 Confirm how to handle orders that were previously pending but are now delivered</t>
-  </si>
-  <si>
-    <t>Currently calculating sum of orders with Pending status based on available data
-Approach is assumption-based due to unclear requirements
-Final validation is subject to business confirmation</t>
   </si>
   <si>
     <t xml:space="preserve">Shipping is at customer level, so we are unable to distinguish order-level Pending vs Delivered status , hence its impossible to get only Pending order amount . 
@@ -1326,12 +1319,108 @@
   <si>
     <t>SELECT SUM(total_amount) FROM (SELECT country, total_transactions,total_amount FROM ( SELECT  c.country, COUNT(o.order_id) AS total_transactions, SUM(o.amount) AS total_amount, RANK() OVER (ORDER BY COUNT(o.order_id), SUM(o.amount)) AS rnk FROM pei.silver.orders o JOIN pei.silver.customers c  ON o.customer_id = c.customer_id GROUP BY c.country ) t WHERE rnk = 1) union all SELECT SUM(total_amount) FROM pei.gold.min_transactions_country ;</t>
   </si>
+  <si>
+    <t>Gap_ID</t>
+  </si>
+  <si>
+    <t>Gap_Description</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Clarification_Required</t>
+  </si>
+  <si>
+    <t>QA_Comment</t>
+  </si>
+  <si>
+    <t>GAP_01</t>
+  </si>
+  <si>
+    <t>Quantity column is not available in source data</t>
+  </si>
+  <si>
+    <t>Total quantity is calculated using count which may not be accurate</t>
+  </si>
+  <si>
+    <t>Tie condition not defined for top product</t>
+  </si>
+  <si>
+    <t>Multiple products may have same purchase count for a country</t>
+  </si>
+  <si>
+    <t>Currently returning all using RANK()</t>
+  </si>
+  <si>
+    <t>Age category boundary not defined</t>
+  </si>
+  <si>
+    <t>Age = 30 may fall into wrong group</t>
+  </si>
+  <si>
+    <t>Currently considered in Above 30</t>
+  </si>
+  <si>
+    <t>Definition of minimum not clear</t>
+  </si>
+  <si>
+    <t>Result may differ if based on transactions or amount</t>
+  </si>
+  <si>
+    <t>Currently using both transactions and amount</t>
+  </si>
+  <si>
+    <t>Shipping is linked using customer_id instead of order_id , it results in multiple shipping records for same customer .</t>
+  </si>
+  <si>
+    <t>Join may create duplicate rows and amount may be counted multiple times .</t>
+  </si>
+  <si>
+    <t>Current logic may gives duplicate data and wrong totals</t>
+  </si>
+  <si>
+    <t>1)Want to check if shipping should be linked at order level for better accuracy.
+2)Want to confirm how we should treat pending status? Should we consider only orders that are not yet delivered?
+3)Want to understand how to identify the latest status of an order? Should we use latest shipping_id or any date field if available?
+4)Since we are showing data at country level, should we include countries with no orders and show 0.00 amount, or skip them?</t>
+  </si>
+  <si>
+    <t>Currently using COUNT(item) as quantity
+Currently grouped by customer and item</t>
+  </si>
+  <si>
+    <t>1)Help us understand how we should calculate quantity, since it is not available in the current data. Should we treat each order as quantity = 1, or is there any other table where we can get actual quantity per order ?
+2)Since quantity is not available, total amount per customer may not fully show the actual purchase (for example, one order may have multiple items but we are counting it as one). Could you please confirm if this approach is okay?
+3)For product details, should we group data by customer and product, or only at customer level? If we group only at customer level, how should we show item details — as a list of products or any other format? A sample output would really help us understand better.
+4)Since we are showing data at customer or customer-product level, should we include all customers even if they have no orders, or only customers who have placed orders?</t>
+  </si>
+  <si>
+    <t>1)Help us understand how we should define "maximum product purchased". Should it be based on number of orders (count) or based on total amount spent on the product?
+2)If two or more products have the same purchase count in a country, how should we handle it? Should we show all such products or only one : as a list of products or any other format? A sample output would really help us understand better.
+3)Since quantity field is not available, we are using count of orders as purchase count. Is there any other table where we can get actual quantity per order ?
+4)If there are no orders for a country, should that country appear in the output or should we skip it?</t>
+  </si>
+  <si>
+    <t>1)Just wanted to confirm how we should define age groups. For example, if age is exactly 30, should it come under below 30 or above 30?
+2)How should we define "most purchased product"? Should it be based on number of orders (count) or based on total amount spent?
+3)If two or more products have the same purchase count in an age group, how should we handle it ? Should we show all products in one record like a list or should we populate in different records .
+4)Since quantity field is not available, we are using count of records as purchase count. Is there any other table where we can get actual quantity per order ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1)If one country has minimum transactions and another country has minimum amount, which one should we return?
+2)If multiple countries have the same minimum value, should we show all of them or only one?
+3)If there are countries with no orders, should we include them with 0 values or skip them?
+4)Since quantity field is not available, we may get incorrect aggregate sum in total_amount field . Is there any other table where we can get actual quantity per order ?
+5)Would it be possible to share a sample output so we can better understand the expected result?
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1356,6 +1445,14 @@
     <font>
       <b/>
       <sz val="24"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1422,7 +1519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1430,16 +1527,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1449,9 +1539,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6456,61 +6549,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D5EAC56-B45B-439F-B2C0-40EF65192417}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="102.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>201</v>
       </c>
     </row>
@@ -6520,6 +6610,455 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86DA3DB-6314-4BE4-9135-2F39FBD9F71E}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E1:E25">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="FAIL">
+      <formula>NOT(ISERROR(SEARCH("FAIL",E1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="PASS">
+      <formula>NOT(ISERROR(SEARCH("PASS",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C494B2D-4917-4F67-B589-44CA545C9720}">
   <dimension ref="A1:R311"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6532,7 +7071,7 @@
   <sheetData>
     <row r="1" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -6554,23 +7093,23 @@
     <row r="18" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>282</v>
+      <c r="A22" s="6" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>283</v>
+      <c r="A23" s="6" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -6591,10 +7130,10 @@
     <row r="39" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="3:18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="5" t="s">
         <v>170</v>
       </c>
     </row>
@@ -6666,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="3:18" x14ac:dyDescent="0.3">
@@ -6695,7 +7234,7 @@
         <v>27</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>175</v>
@@ -6732,7 +7271,7 @@
         <v>43</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>175</v>
@@ -6742,12 +7281,12 @@
         <v>1</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="3:18" x14ac:dyDescent="0.3">
       <c r="R48" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -6756,170 +7295,170 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>284</v>
+      <c r="A53" s="6" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="14"/>
+      <c r="O69" s="14"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="6" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="6" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="7" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="6" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="7" t="s">
-        <v>291</v>
-      </c>
-    </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" s="7" t="s">
-        <v>294</v>
+      <c r="A193" s="6" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="217" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A217" s="7" t="s">
+      <c r="A217" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" s="6" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A242" s="7" t="s">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A266" s="6" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A266" s="7" t="s">
-        <v>301</v>
-      </c>
-    </row>
     <row r="291" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A291" s="7" t="s">
-        <v>302</v>
+      <c r="A291" s="6" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="311" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A311" s="7" t="s">
-        <v>315</v>
+      <c r="A311" s="6" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -6939,7 +7478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A4575AB-49B4-465B-83B3-C2560581AECF}">
   <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6972,7 +7511,7 @@
         <v>78</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>39</v>
@@ -7020,7 +7559,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>102</v>
@@ -7037,7 +7576,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>108</v>
@@ -7054,7 +7593,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>114</v>
@@ -7071,7 +7610,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>134</v>
@@ -7088,10 +7627,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>39</v>
@@ -7105,10 +7644,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>39</v>
@@ -7122,7 +7661,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>146</v>
@@ -7139,10 +7678,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>39</v>
@@ -7156,10 +7695,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>39</v>
@@ -7173,10 +7712,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>39</v>
@@ -7190,10 +7729,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>39</v>
@@ -7207,10 +7746,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>314</v>
+        <v>299</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>39</v>
@@ -7224,9 +7763,9 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B17" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -7241,9 +7780,9 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B18" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -7269,7 +7808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{945EE4F3-F6C5-48E2-8A7E-2DCED45DE3C0}">
   <dimension ref="A1:R291"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7282,7 +7821,7 @@
   <sheetData>
     <row r="1" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>83</v>
       </c>
     </row>
@@ -7304,23 +7843,23 @@
     <row r="18" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>326</v>
+      <c r="A23" s="6" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -7341,10 +7880,10 @@
     <row r="39" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="3:18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="5" t="s">
         <v>170</v>
       </c>
     </row>
@@ -7406,7 +7945,7 @@
         <v>48</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>175</v>
@@ -7416,7 +7955,7 @@
         <v>1</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="46" spans="3:18" x14ac:dyDescent="0.3">
@@ -7445,7 +7984,7 @@
         <v>27</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>175</v>
@@ -7455,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="3:18" x14ac:dyDescent="0.3">
@@ -7482,7 +8021,7 @@
         <v>43</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>175</v>
@@ -7492,12 +8031,12 @@
         <v>1</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="3:18" x14ac:dyDescent="0.3">
       <c r="R48" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -7511,165 +8050,165 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>327</v>
+      <c r="A53" s="6" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="14"/>
+      <c r="O69" s="14"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="6" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="6" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="7" t="s">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="6" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" s="7" t="s">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="6" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" s="6" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A217" s="7" t="s">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A266" s="6" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A242" s="7" t="s">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A291" s="6" t="s">
         <v>337</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A266" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A291" s="7" t="s">
-        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -7689,7 +8228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE02936-9355-4A36-B179-DFD447E17342}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7722,7 +8261,7 @@
         <v>83</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>47</v>
@@ -7787,7 +8326,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>108</v>
@@ -7804,7 +8343,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>114</v>
@@ -7821,7 +8360,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>134</v>
@@ -7838,10 +8377,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>47</v>
@@ -7855,10 +8394,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>47</v>
@@ -7872,10 +8411,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>47</v>
@@ -7889,10 +8428,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>293</v>
+        <v>331</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>47</v>
@@ -7906,10 +8445,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>296</v>
+        <v>333</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>47</v>
@@ -7923,10 +8462,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>298</v>
+        <v>334</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>47</v>
@@ -7940,10 +8479,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>314</v>
+        <v>335</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>312</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>47</v>
@@ -7957,9 +8496,9 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B16" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -7974,9 +8513,9 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B17" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -8002,7 +8541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B663B89-432B-4F32-8B49-46391610DBF8}">
   <dimension ref="A1:P372"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8015,7 +8554,7 @@
   <sheetData>
     <row r="1" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>88</v>
       </c>
     </row>
@@ -8037,23 +8576,23 @@
     <row r="18" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>358</v>
+      <c r="A23" s="6" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -8074,14 +8613,14 @@
     <row r="39" spans="3:16" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="3:16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="P40" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="3:16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="5" t="s">
         <v>170</v>
       </c>
       <c r="P41" t="s">
@@ -8090,7 +8629,7 @@
     </row>
     <row r="42" spans="3:16" x14ac:dyDescent="0.3">
       <c r="P42" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="3:16" x14ac:dyDescent="0.3">
@@ -8190,7 +8729,7 @@
         <v>31</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>175</v>
@@ -8226,7 +8765,7 @@
         <v>12</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>175</v>
@@ -8237,185 +8776,185 @@
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>359</v>
+      <c r="A53" s="6" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="14"/>
+      <c r="O69" s="14"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" s="6" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="6" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A150" s="6" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A171" s="6" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="7" t="s">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A193" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" s="7" t="s">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A217" s="6" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A217" s="7" t="s">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A242" s="6" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A242" s="7" t="s">
-        <v>371</v>
-      </c>
-    </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A266" s="7" t="s">
-        <v>374</v>
+      <c r="A266" s="6" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="286" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A286" s="7" t="s">
-        <v>375</v>
+      <c r="A286" s="6" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="307" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A307" s="7" t="s">
+      <c r="A307" s="6" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A327" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A347" s="6" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A327" s="7" t="s">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A372" s="6" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A347" s="7" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A372" s="7" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -8435,7 +8974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85207443-8FEA-45ED-9A66-ECC6C1B61E4E}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8456,7 +8995,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -8468,12 +9007,12 @@
         <v>88</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="11" t="s">
         <v>95</v>
       </c>
       <c r="E2" s="3" t="s">
@@ -8490,7 +9029,7 @@
       <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -8507,7 +9046,7 @@
       <c r="C4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="11" t="s">
         <v>100</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -8524,7 +9063,7 @@
       <c r="C5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="11" t="s">
         <v>103</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -8533,7 +9072,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>108</v>
@@ -8541,7 +9080,7 @@
       <c r="C6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="11" t="s">
         <v>109</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -8550,7 +9089,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>114</v>
@@ -8558,7 +9097,7 @@
       <c r="C7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="11" t="s">
         <v>115</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -8567,7 +9106,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>134</v>
@@ -8575,7 +9114,7 @@
       <c r="C8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="11" t="s">
         <v>118</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -8584,15 +9123,15 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="11" t="s">
         <v>121</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -8601,15 +9140,15 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="11" t="s">
         <v>118</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -8618,15 +9157,15 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="11" t="s">
         <v>118</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -8635,15 +9174,15 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>227</v>
+        <v>363</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="11" t="s">
         <v>149</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -8652,15 +9191,15 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>229</v>
+        <v>365</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="11" t="s">
         <v>152</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -8669,15 +9208,15 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>231</v>
+        <v>367</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="11" t="s">
         <v>155</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -8686,15 +9225,15 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>373</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="11" t="s">
         <v>159</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -8703,15 +9242,15 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>242</v>
+        <v>372</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="11" t="s">
         <v>149</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -8720,15 +9259,15 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>243</v>
+        <v>373</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="11" t="s">
         <v>152</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -8737,15 +9276,15 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>245</v>
+        <v>396</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="11" t="s">
         <v>155</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -8754,15 +9293,15 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="B19" s="11" t="s">
         <v>397</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>395</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="11" t="s">
         <v>159</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -8771,15 +9310,15 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B20" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="11" t="s">
         <v>128</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -8788,15 +9327,15 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B21" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>130</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="11" t="s">
         <v>118</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -8818,503 +9357,556 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1008E9C9-909F-4323-A504-2DBF27662DB8}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9340,8 +9932,222 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74799290-25C7-4185-9ACE-0EA28E5C1443}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="5" max="5" width="58.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2839FD62-2A6C-4A53-8548-2FB7611B952C}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.44140625" customWidth="1"/>
+    <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D1" t="s">
+        <v>407</v>
+      </c>
+      <c r="E1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="E2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" t="s">
+        <v>413</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="E4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="E5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C6" t="s">
+        <v>406</v>
+      </c>
+      <c r="D6" t="s">
+        <v>407</v>
+      </c>
+      <c r="E6" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="E7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E078F76-DA5E-43E0-BF21-22AC5986C891}">
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" style="1" customWidth="1"/>
@@ -9352,171 +10158,67 @@
     <col min="7" max="7" width="24.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="106" style="1" customWidth="1"/>
     <col min="9" max="9" width="56.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="47.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="5"/>
+    <col min="10" max="10" width="47.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I5" s="10" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>66</v>
@@ -9524,28 +10226,28 @@
       <c r="G6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>109</v>
+      <c r="H6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>66</v>
@@ -9553,28 +10255,28 @@
       <c r="G7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>115</v>
+      <c r="H7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>66</v>
@@ -9583,27 +10285,27 @@
         <v>11</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>118</v>
+        <v>106</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>66</v>
@@ -9612,27 +10314,27 @@
         <v>11</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>121</v>
+        <v>106</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>66</v>
@@ -9641,27 +10343,27 @@
         <v>11</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>118</v>
+        <v>106</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>66</v>
@@ -9669,28 +10371,28 @@
       <c r="G11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>118</v>
+      <c r="H11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>144</v>
+      <c r="C12" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>66</v>
@@ -9698,28 +10400,28 @@
       <c r="G12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>149</v>
+      <c r="H12" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>144</v>
+      <c r="C13" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>66</v>
@@ -9727,28 +10429,28 @@
       <c r="G13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>152</v>
+      <c r="H13" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>144</v>
+      <c r="C14" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>66</v>
@@ -9756,28 +10458,28 @@
       <c r="G14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>155</v>
+      <c r="H14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="9" t="s">
-        <v>144</v>
+      <c r="C15" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>66</v>
@@ -9785,28 +10487,28 @@
       <c r="G15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>159</v>
+      <c r="H15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>143</v>
+      <c r="C16" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>66</v>
@@ -9815,27 +10517,27 @@
         <v>11</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>128</v>
+        <v>184</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="7" t="s">
         <v>144</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>66</v>
@@ -9843,898 +10545,922 @@
       <c r="G17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I21" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B27" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G27" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I27" s="10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B28" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D28" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E28" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="I30" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G31" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H31" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I24" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="20" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="11" t="s">
+      <c r="I34" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="F25" s="11" t="s">
+      <c r="C35" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="I25" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="11" t="s">
+      <c r="H35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F26" s="11" t="s">
+      <c r="C36" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G36" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="11" t="s">
+      <c r="H36" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F27" s="11" t="s">
+      <c r="C37" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G37" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="11" t="s">
+      <c r="H37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="11" t="s">
+      <c r="C38" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G38" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="I28" s="19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="20" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="H38" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29" s="11" t="s">
+      <c r="C39" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H39" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I29" s="19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="B44" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="F30" s="11" t="s">
+      <c r="C44" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="I30" s="19" t="s">
+      <c r="H44" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I51" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="20" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="I32" s="19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="20" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="I33" s="19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="I34" s="19" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="I35" s="19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="I37" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="I38" s="19" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="I39" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="I40" s="16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="I41" s="16" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G42" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I42" s="16" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G43" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="I43" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="I44" s="16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="I45" s="16" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="I46" s="16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="I47" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G57" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H57" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I53" s="15" t="s">
+      <c r="I57" s="10" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="I54" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="I55" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="I56" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="I57" s="16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>283</v>
+        <v>78</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>108</v>
+        <v>277</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>80</v>
@@ -10742,28 +11468,28 @@
       <c r="G58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H58" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="I58" s="16" t="s">
-        <v>109</v>
+      <c r="H58" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>284</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>80</v>
@@ -10771,28 +11497,28 @@
       <c r="G59" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H59" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="I59" s="16" t="s">
-        <v>115</v>
+      <c r="H59" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>80</v>
@@ -10801,27 +11527,27 @@
         <v>39</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="I60" s="16" t="s">
-        <v>118</v>
+        <v>279</v>
+      </c>
+      <c r="I60" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="11" t="s">
-        <v>141</v>
+      <c r="C61" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>307</v>
+        <v>102</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>80</v>
@@ -10830,27 +11556,27 @@
         <v>39</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I61" s="16" t="s">
-        <v>121</v>
+        <v>301</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>80</v>
@@ -10859,27 +11585,27 @@
         <v>39</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="I62" s="16" t="s">
-        <v>118</v>
+        <v>279</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>80</v>
@@ -10887,16 +11613,16 @@
       <c r="G63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H63" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="I63" s="16" t="s">
-        <v>118</v>
+      <c r="H63" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>79</v>
@@ -10905,10 +11631,10 @@
         <v>141</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>311</v>
+        <v>133</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>312</v>
+        <v>134</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>80</v>
@@ -10916,16 +11642,16 @@
       <c r="G64" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H64" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="I64" s="16" t="s">
+      <c r="H64" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="I64" s="11" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>79</v>
@@ -10934,10 +11660,10 @@
         <v>141</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>293</v>
+        <v>74</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>80</v>
@@ -10945,28 +11671,28 @@
       <c r="G65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H65" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="I65" s="16" t="s">
-        <v>149</v>
+      <c r="H65" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>296</v>
+        <v>122</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>80</v>
@@ -10974,16 +11700,16 @@
       <c r="G66" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H66" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="I66" s="16" t="s">
-        <v>152</v>
+      <c r="H66" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>79</v>
@@ -10992,10 +11718,10 @@
         <v>141</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>298</v>
+        <v>145</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>80</v>
@@ -11003,16 +11729,16 @@
       <c r="G67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H67" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="I67" s="16" t="s">
-        <v>155</v>
+      <c r="H67" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>79</v>
@@ -11021,10 +11747,10 @@
         <v>141</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>314</v>
+        <v>309</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>80</v>
@@ -11032,28 +11758,28 @@
       <c r="G68" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H68" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="I68" s="16" t="s">
-        <v>159</v>
+      <c r="H68" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>126</v>
+        <v>290</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>80</v>
@@ -11061,28 +11787,28 @@
       <c r="G69" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H69" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="I69" s="16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="H69" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E70" s="11" t="s">
-        <v>130</v>
+        <v>293</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>80</v>
@@ -11090,173 +11816,185 @@
       <c r="G70" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H70" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="I70" s="16" t="s">
+      <c r="H70" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I74" s="11" t="s">
         <v>118</v>
       </c>
     </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="13"/>
+      <c r="C77" s="13"/>
+    </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="13"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G82" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H78" s="2" t="s">
+      <c r="H82" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I78" s="15" t="s">
+      <c r="I82" s="10" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I79" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="I80" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="I81" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="I82" s="16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>326</v>
+        <v>83</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>108</v>
+        <v>321</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>80</v>
@@ -11264,28 +12002,28 @@
       <c r="G83" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H83" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="I83" s="16" t="s">
-        <v>109</v>
+      <c r="H83" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>85</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>80</v>
@@ -11293,28 +12031,28 @@
       <c r="G84" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H84" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="I84" s="16" t="s">
-        <v>115</v>
+      <c r="H84" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>328</v>
+        <v>86</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>80</v>
@@ -11323,27 +12061,27 @@
         <v>47</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="I85" s="16" t="s">
-        <v>118</v>
+        <v>323</v>
+      </c>
+      <c r="I85" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>330</v>
+        <v>87</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C86" s="11" t="s">
-        <v>141</v>
+      <c r="C86" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>346</v>
+        <v>102</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>80</v>
@@ -11352,27 +12090,27 @@
         <v>47</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="I86" s="16" t="s">
-        <v>121</v>
+        <v>323</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>347</v>
+        <v>108</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>80</v>
@@ -11381,27 +12119,27 @@
         <v>47</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="I87" s="16" t="s">
-        <v>118</v>
+        <v>323</v>
+      </c>
+      <c r="I87" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>311</v>
+        <v>113</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>312</v>
+        <v>114</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>80</v>
@@ -11409,16 +12147,16 @@
       <c r="G88" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H88" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="I88" s="16" t="s">
-        <v>118</v>
+      <c r="H88" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I88" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>84</v>
@@ -11427,10 +12165,10 @@
         <v>141</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>293</v>
+        <v>133</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>80</v>
@@ -11438,16 +12176,16 @@
       <c r="G89" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H89" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="I89" s="16" t="s">
-        <v>149</v>
+      <c r="H89" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I89" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>84</v>
@@ -11456,10 +12194,10 @@
         <v>141</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>296</v>
+        <v>74</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>80</v>
@@ -11467,28 +12205,28 @@
       <c r="G90" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H90" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="I90" s="16" t="s">
-        <v>152</v>
+      <c r="H90" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="I90" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>298</v>
+        <v>122</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>80</v>
@@ -11496,16 +12234,16 @@
       <c r="G91" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H91" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="I91" s="16" t="s">
-        <v>155</v>
+      <c r="H91" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I91" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>84</v>
@@ -11514,10 +12252,10 @@
         <v>141</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>314</v>
+        <v>309</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>80</v>
@@ -11525,28 +12263,28 @@
       <c r="G92" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H92" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="I92" s="16" t="s">
-        <v>159</v>
+      <c r="H92" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I92" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E93" s="11" t="s">
-        <v>126</v>
+        <v>290</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>80</v>
@@ -11554,28 +12292,28 @@
       <c r="G93" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H93" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="I93" s="16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H93" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I93" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>84</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>130</v>
+        <v>293</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>80</v>
@@ -11583,173 +12321,185 @@
       <c r="G94" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H94" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="I94" s="16" t="s">
+      <c r="H94" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="I94" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I95" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="I96" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I97" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I98" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B102" s="13"/>
+      <c r="C102" s="13"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="13"/>
+      <c r="B103" s="13"/>
+      <c r="C103" s="13"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B108" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E104" s="2" t="s">
+      <c r="E108" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F104" s="2" t="s">
+      <c r="F108" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="G108" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H104" s="2" t="s">
+      <c r="H108" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I104" s="15" t="s">
+      <c r="I108" s="10" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I105" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="I106" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="I107" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="I108" s="16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>358</v>
+        <v>88</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>108</v>
+        <v>384</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>80</v>
@@ -11757,28 +12507,28 @@
       <c r="G109" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H109" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="I109" s="16" t="s">
-        <v>109</v>
+      <c r="H109" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I109" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>80</v>
@@ -11786,28 +12536,28 @@
       <c r="G110" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H110" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="I110" s="16" t="s">
-        <v>115</v>
+      <c r="H110" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="I110" s="11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>360</v>
+        <v>91</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>80</v>
@@ -11816,27 +12566,27 @@
         <v>52</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="I111" s="16" t="s">
-        <v>118</v>
+        <v>355</v>
+      </c>
+      <c r="I111" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>362</v>
+        <v>92</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C112" s="11" t="s">
-        <v>141</v>
+      <c r="C112" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>380</v>
+        <v>102</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>80</v>
@@ -11845,27 +12595,27 @@
         <v>52</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="I112" s="16" t="s">
-        <v>121</v>
+        <v>355</v>
+      </c>
+      <c r="I112" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>382</v>
+        <v>108</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>80</v>
@@ -11874,27 +12624,27 @@
         <v>52</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="I113" s="16" t="s">
-        <v>118</v>
+        <v>355</v>
+      </c>
+      <c r="I113" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>311</v>
+        <v>113</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>384</v>
+        <v>114</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>80</v>
@@ -11902,16 +12652,16 @@
       <c r="G114" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H114" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="I114" s="16" t="s">
-        <v>118</v>
+      <c r="H114" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I114" s="11" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>89</v>
@@ -11920,10 +12670,10 @@
         <v>141</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>227</v>
+        <v>133</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>80</v>
@@ -11931,16 +12681,16 @@
       <c r="G115" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H115" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="I115" s="16" t="s">
-        <v>149</v>
+      <c r="H115" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="I115" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>89</v>
@@ -11949,10 +12699,10 @@
         <v>141</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="E116" s="11" t="s">
-        <v>229</v>
+        <v>74</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>80</v>
@@ -11960,28 +12710,28 @@
       <c r="G116" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H116" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="I116" s="16" t="s">
-        <v>152</v>
+      <c r="H116" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I116" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="E117" s="11" t="s">
-        <v>231</v>
+        <v>122</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>80</v>
@@ -11989,16 +12739,16 @@
       <c r="G117" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H117" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="I117" s="16" t="s">
-        <v>155</v>
+      <c r="H117" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="I117" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>89</v>
@@ -12007,10 +12757,10 @@
         <v>141</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E118" s="11" t="s">
-        <v>373</v>
+        <v>309</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>382</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>80</v>
@@ -12018,16 +12768,16 @@
       <c r="G118" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H118" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="I118" s="16" t="s">
-        <v>159</v>
+      <c r="H118" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I118" s="11" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>89</v>
@@ -12036,10 +12786,10 @@
         <v>141</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E119" s="11" t="s">
-        <v>242</v>
+        <v>364</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>225</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>80</v>
@@ -12047,16 +12797,16 @@
       <c r="G119" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H119" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="I119" s="16" t="s">
+      <c r="H119" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I119" s="11" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>89</v>
@@ -12065,10 +12815,10 @@
         <v>141</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E120" s="11" t="s">
-        <v>243</v>
+        <v>366</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>80</v>
@@ -12076,16 +12826,16 @@
       <c r="G120" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H120" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="I120" s="16" t="s">
+      <c r="H120" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I120" s="11" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>89</v>
@@ -12094,10 +12844,10 @@
         <v>141</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="E121" s="11" t="s">
-        <v>245</v>
+        <v>368</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>80</v>
@@ -12105,16 +12855,16 @@
       <c r="G121" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H121" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="I121" s="16" t="s">
+      <c r="H121" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="I121" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>89</v>
@@ -12123,10 +12873,10 @@
         <v>141</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E122" s="11" t="s">
-        <v>397</v>
+        <v>370</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>80</v>
@@ -12134,28 +12884,28 @@
       <c r="G122" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H122" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="I122" s="16" t="s">
+      <c r="H122" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="I122" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E123" s="11" t="s">
-        <v>126</v>
+        <v>391</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>240</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>80</v>
@@ -12163,28 +12913,28 @@
       <c r="G123" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H123" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="I123" s="16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H123" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="I123" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E124" s="11" t="s">
-        <v>130</v>
+        <v>392</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>80</v>
@@ -12192,23 +12942,144 @@
       <c r="G124" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H124" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="I124" s="16" t="s">
+      <c r="H124" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I124" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="I125" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="I126" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="I127" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I128" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="125" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="126" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A23:C24"/>
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="A77:C78"/>
+    <mergeCell ref="A102:C103"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130428D2-44A4-4333-A030-816987B279E0}">
   <dimension ref="A1:R349"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12221,7 +13092,7 @@
   <sheetData>
     <row r="1" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
     </row>
@@ -12243,22 +13114,22 @@
     <row r="18" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>111</v>
       </c>
     </row>
@@ -12280,10 +13151,10 @@
     <row r="39" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="3:18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="5" t="s">
         <v>170</v>
       </c>
     </row>
@@ -12413,164 +13284,164 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="14"/>
+      <c r="O69" s="14"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="6" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
+      <c r="A131" s="6" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="6" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="7" t="s">
+      <c r="A171" s="6" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="209" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A209" s="7" t="s">
+      <c r="A209" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="244" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A244" s="7" t="s">
+      <c r="A244" s="6" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A278" s="7" t="s">
+      <c r="A278" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="312" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A312" s="7" t="s">
+      <c r="A312" s="6" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A349" s="7" t="s">
+      <c r="A349" s="6" t="s">
         <v>161</v>
       </c>
     </row>
@@ -12591,7 +13462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0B8795-6099-4589-82DE-44E5865F3D68}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12904,55 +13775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74799290-25C7-4185-9ACE-0EA28E5C1443}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="70.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="58.88671875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
-        <v>213</v>
-      </c>
-      <c r="D1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>216</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D34FC2-A0E0-4A3E-A566-3589776D6182}">
   <dimension ref="A1:R424"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12965,7 +13788,7 @@
   <sheetData>
     <row r="1" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -12987,22 +13810,22 @@
     <row r="18" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>77</v>
       </c>
     </row>
@@ -13024,10 +13847,10 @@
     <row r="39" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="40" spans="3:18" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="41" spans="3:18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="5" t="s">
         <v>170</v>
       </c>
     </row>
@@ -13087,7 +13910,7 @@
         <v>23</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>175</v>
@@ -13097,7 +13920,7 @@
         <v>1</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="3:18" x14ac:dyDescent="0.3">
@@ -13126,7 +13949,7 @@
         <v>27</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>175</v>
@@ -13136,7 +13959,7 @@
         <v>1</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="3:18" x14ac:dyDescent="0.3">
@@ -13163,7 +13986,7 @@
         <v>31</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>175</v>
@@ -13173,7 +13996,7 @@
         <v>1</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="3:18" x14ac:dyDescent="0.3">
@@ -13200,7 +14023,7 @@
         <v>34</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>175</v>
@@ -13210,7 +14033,7 @@
         <v>1</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
@@ -13249,7 +14072,7 @@
         <v>1</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.3">
@@ -13263,205 +14086,205 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" s="14"/>
+      <c r="N68" s="14"/>
+      <c r="O68" s="14"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="14"/>
+      <c r="L69" s="14"/>
+      <c r="M69" s="14"/>
+      <c r="N69" s="14"/>
+      <c r="O69" s="14"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" s="14"/>
+      <c r="N70" s="14"/>
+      <c r="O70" s="14"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" s="14"/>
+      <c r="N71" s="14"/>
+      <c r="O71" s="14"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
+      <c r="N72" s="14"/>
+      <c r="O72" s="14"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
+      <c r="N73" s="14"/>
+      <c r="O73" s="14"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" s="14"/>
+      <c r="N74" s="14"/>
+      <c r="O74" s="14"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="6" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="6" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
+      <c r="A131" s="6" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="6" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171" s="7" t="s">
+      <c r="A171" s="6" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A196" s="7" t="s">
+      <c r="A196" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="218" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A218" s="7" t="s">
+      <c r="A218" s="6" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A238" s="7" t="s">
+      <c r="A238" s="6" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="259" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A259" s="7" t="s">
+      <c r="A259" s="6" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A276" s="7" t="s">
+      <c r="A276" s="6" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="293" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A293" s="7" t="s">
+      <c r="A293" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A317" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A335" s="6" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A317" s="7" t="s">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A352" s="6" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A335" s="7" t="s">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A369" s="6" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A352" s="7" t="s">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A386" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A369" s="7" t="s">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A403" s="6" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A386" s="7" t="s">
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A424" s="6" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A403" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A424" s="7" t="s">
-        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -13479,453 +14302,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86DA3DB-6314-4BE4-9135-2F39FBD9F71E}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="E1:E25">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="FAIL">
-      <formula>NOT(ISERROR(SEARCH("FAIL",E1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="PASS">
-      <formula>NOT(ISERROR(SEARCH("PASS",E1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/silver_to_gold_validation.xlsx
+++ b/silver_to_gold_validation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uthej\Downloads\PEI_assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025AE63E-5387-418F-931B-D0686D6AE22E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE55B3A6-26F0-4753-9811-5A5F4EE24BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="16" xr2:uid="{BC5507A9-D27E-444C-93EA-C153FA16561C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BC5507A9-D27E-444C-93EA-C153FA16561C}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet index - content" sheetId="22" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="520">
   <si>
     <t>Source_Table</t>
   </si>
@@ -1260,411 +1260,455 @@
     <t>Clarification_Required</t>
   </si>
   <si>
-    <t>1)Want to check if shipping should be linked at order level for better accuracy.
-2)Want to confirm how we should treat pending status? Should we consider only orders that are not yet delivered?
-3)Want to understand how to identify the latest status of an order? Should we use latest shipping_id or any date field if available?
-4)Since we are showing data at country level, should we include countries with no orders and show 0.00 amount, or skip them?</t>
-  </si>
-  <si>
-    <t>1)Help us understand how we should calculate quantity, since it is not available in the current data. Should we treat each order as quantity = 1, or is there any other table where we can get actual quantity per order ?
-2)Since quantity is not available, total amount per customer may not fully show the actual purchase (for example, one order may have multiple items but we are counting it as one). Could you please confirm if this approach is okay?
-3)For product details, should we group data by customer and product, or only at customer level? If we group only at customer level, how should we show item details — as a list of products or any other format? A sample output would really help us understand better.
-4)Since we are showing data at customer or customer-product level, should we include all customers even if they have no orders, or only customers who have placed orders?</t>
-  </si>
-  <si>
     <t>1)Help us understand how we should define "maximum product purchased". Should it be based on number of orders (count) or based on total amount spent on the product?
 2)If two or more products have the same purchase count in a country, how should we handle it? Should we show all such products or only one : as a list of products or any other format? A sample output would really help us understand better.
 3)Since quantity field is not available, we are using count of orders as purchase count. Is there any other table where we can get actual quantity per order ?
 4)If there are no orders for a country, should that country appear in the output or should we skip it?</t>
   </si>
   <si>
-    <t>1)Just wanted to confirm how we should define age groups. For example, if age is exactly 30, should it come under below 30 or above 30?
-2)How should we define "most purchased product"? Should it be based on number of orders (count) or based on total amount spent?
-3)If two or more products have the same purchase count in an age group, how should we handle it ? Should we show all products in one record like a list or should we populate in different records .
-4)Since quantity field is not available, we are using count of records as purchase count. Is there any other table where we can get actual quantity per order ?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1)If one country has minimum transactions and another country has minimum amount, which one should we return?
-2)If multiple countries have the same minimum value, should we show all of them or only one?
-3)If there are countries with no orders, should we include them with 0 values or skip them?
-4)Since quantity field is not available, we may get incorrect aggregate sum in total_amount field . Is there any other table where we can get actual quantity per order ?
-5)Would it be possible to share a sample output so we can better understand the expected result?
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Requirement 1 pending amount by country</t>
+  </si>
+  <si>
+    <t>Requirement 2 customer product summary</t>
+  </si>
+  <si>
+    <t>Requirement 3 top product by country</t>
+  </si>
+  <si>
+    <t>Requirement 4 top product by age group</t>
+  </si>
+  <si>
+    <t>Requirement 5 minimum transaction country</t>
+  </si>
+  <si>
+    <t>Approach</t>
+  </si>
+  <si>
+    <t>Data_Validation</t>
+  </si>
+  <si>
+    <t>Schema_Validation</t>
+  </si>
+  <si>
+    <t>Check grouping logic</t>
+  </si>
+  <si>
+    <t>Entry_Criteria</t>
+  </si>
+  <si>
+    <t>Gold tables are created</t>
+  </si>
+  <si>
+    <t>Exit_Criteria</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t>Databricks</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>PySpark</t>
+  </si>
+  <si>
+    <t>Check data is correctly transformed from silver tables to gold tables</t>
+  </si>
+  <si>
+    <t>Check joins between tables</t>
+  </si>
+  <si>
+    <t>Check business logic</t>
+  </si>
+  <si>
+    <t>Validate using SQL queries</t>
+  </si>
+  <si>
+    <t>Check column names</t>
+  </si>
+  <si>
+    <t>Check data types</t>
+  </si>
+  <si>
+    <t>Check column mapping</t>
+  </si>
+  <si>
+    <t>Check row count match</t>
+  </si>
+  <si>
+    <t>Check sum min max avg values</t>
+  </si>
+  <si>
+    <t>Check no duplicate records</t>
+  </si>
+  <si>
+    <t>Check no null values</t>
+  </si>
+  <si>
+    <t>Transformation_Check</t>
+  </si>
+  <si>
+    <t>Check ranking logic</t>
+  </si>
+  <si>
+    <t>Business_Check</t>
+  </si>
+  <si>
+    <t>Validate all 5 requirements logic</t>
+  </si>
+  <si>
+    <t>Silver tables are ready</t>
+  </si>
+  <si>
+    <t>All tests completed</t>
+  </si>
+  <si>
+    <t>Results are correct</t>
+  </si>
+  <si>
+    <t>Customers ,Orders and Shipping to Gold tables</t>
+  </si>
+  <si>
+    <t>Check aggregations like sum,min,max,avg and count</t>
+  </si>
+  <si>
+    <t>Check filters like pending status and rank</t>
+  </si>
+  <si>
+    <t>Total_Test_Cases</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Bugs_Found</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>All validations passed successfully</t>
+  </si>
+  <si>
+    <t>REQ1</t>
+  </si>
+  <si>
+    <t>REQ2</t>
+  </si>
+  <si>
+    <t>REQ3</t>
+  </si>
+  <si>
+    <t>REQ4</t>
+  </si>
+  <si>
+    <t>REQ5</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Total_Requirements</t>
+  </si>
+  <si>
+    <t>Total_Test_Cases_Executed</t>
+  </si>
+  <si>
+    <t>Total_Test_Cases_Passed</t>
+  </si>
+  <si>
+    <t>Total_Test_Cases_Failed</t>
+  </si>
+  <si>
+    <t>Execution_Status</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Requirement_1_Test_Cases</t>
+  </si>
+  <si>
+    <t>Requirement_1_Passed</t>
+  </si>
+  <si>
+    <t>Requirement_1_Failed</t>
+  </si>
+  <si>
+    <t>Requirement_2_Test_Cases</t>
+  </si>
+  <si>
+    <t>Requirement_2_Passed</t>
+  </si>
+  <si>
+    <t>Requirement_2_Failed</t>
+  </si>
+  <si>
+    <t>Requirement_3_Test_Cases</t>
+  </si>
+  <si>
+    <t>Requirement_3_Passed</t>
+  </si>
+  <si>
+    <t>Requirement_3_Failed</t>
+  </si>
+  <si>
+    <t>Requirement_4_Test_Cases</t>
+  </si>
+  <si>
+    <t>Requirement_4_Passed</t>
+  </si>
+  <si>
+    <t>Requirement_4_Failed</t>
+  </si>
+  <si>
+    <t>Requirement_5_Test_Cases</t>
+  </si>
+  <si>
+    <t>Requirement_5_Passed</t>
+  </si>
+  <si>
+    <t>Requirement_5_Failed</t>
+  </si>
+  <si>
+    <t>Total_Defects</t>
+  </si>
+  <si>
+    <t>High_Severity_Defects</t>
+  </si>
+  <si>
+    <t>Medium_Severity_Defects</t>
+  </si>
+  <si>
+    <t>Low_Severity_Defects</t>
+  </si>
+  <si>
+    <t>All test cases passed successfully. No defects found. Any risks are documented as requirement gaps.</t>
+  </si>
+  <si>
+    <t>schema map silver to gold</t>
+  </si>
+  <si>
+    <t>metrics-summary</t>
+  </si>
+  <si>
+    <t>List of all 5 requirements to be built in gold layer</t>
+  </si>
+  <si>
+    <t>Simple plan to test data from silver to gold tables</t>
+  </si>
+  <si>
+    <t>List of questions and gaps found in requirements</t>
+  </si>
+  <si>
+    <t>Mapping of columns from silver tables to gold tables</t>
+  </si>
+  <si>
+    <t>All test cases for all 5 requirements</t>
+  </si>
+  <si>
+    <t>Summary of total test cases and results</t>
+  </si>
+  <si>
+    <t>Final output for Requirement 1</t>
+  </si>
+  <si>
+    <t>Final output for Requirement 2</t>
+  </si>
+  <si>
+    <t>Final output for Requirement 3</t>
+  </si>
+  <si>
+    <t>Final output for Requirement 4</t>
+  </si>
+  <si>
+    <t>Final output for Requirement 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheet Name </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Description</t>
+  </si>
+  <si>
+    <t>Sheet Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details of bugs found during testing </t>
+  </si>
+  <si>
+    <t>Test execution  of Requirement 1 test cases</t>
+  </si>
+  <si>
+    <t>Test execution  of Requirement 2 test cases</t>
+  </si>
+  <si>
+    <t>Test execution  of Requirement 3 test cases</t>
+  </si>
+  <si>
+    <t>Test execution  of Requirement 4 test cases</t>
+  </si>
+  <si>
+    <t>Test execution  of Requirement 5 test cases</t>
+  </si>
+  <si>
+    <t>Business Requirements'!A1</t>
+  </si>
+  <si>
+    <t>testplan - silver to gold'!A1</t>
+  </si>
+  <si>
+    <t>Gaps-Requirement gathering'!A1</t>
+  </si>
+  <si>
+    <t>schema map silver to gold'!A1</t>
+  </si>
+  <si>
+    <t>test cases'!A1</t>
+  </si>
+  <si>
+    <t>bug report'!A1</t>
+  </si>
+  <si>
+    <t>metrics-summary'!A1</t>
+  </si>
+  <si>
+    <t>REQ1_test_execution!A1</t>
+  </si>
+  <si>
+    <t>REQ1_test_final_results!A1</t>
+  </si>
+  <si>
+    <t>REQ2_test_execution!A1</t>
+  </si>
+  <si>
+    <t>REQ2_test_final_results!A1</t>
+  </si>
+  <si>
+    <t>REQ3_test_execution!A1</t>
+  </si>
+  <si>
+    <t>REQ3_test_final_results!A1</t>
+  </si>
+  <si>
+    <t>REQ4_test_execution!A1</t>
+  </si>
+  <si>
+    <t>REQ4_test_final_results!A1</t>
+  </si>
+  <si>
+    <t>REQ5_test_execution!A1</t>
+  </si>
+  <si>
+    <t>REQ5_test_final_results!A1</t>
+  </si>
+  <si>
+    <t>Business Requirements</t>
+  </si>
+  <si>
+    <t>testplan - silver to gold</t>
+  </si>
+  <si>
+    <t>Gaps-Requirement gathering</t>
+  </si>
+  <si>
+    <t>test cases</t>
+  </si>
+  <si>
+    <t>bug report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA comments </t>
+  </si>
+  <si>
+    <t>1) Since quantity is not available, each order is treated as quantity = 1
+2) Total transactions = count of order_id
+3) Total quantity = count of item (same as number of records)
+4) Data is grouped by customer_id and item (customer-product level)
+5) Only customers with orders are included
+6) Total amount is calculated using SUM(amount)</t>
+  </si>
+  <si>
+    <t>1) Maximum product purchased is calculated based on count of orders
+2) Purchase count = COUNT(*) of orders
+3) RANK() is used to get top product per country
+4) If multiple products have same count, all are returned
+5) Only countries with orders are included (no empty countries)</t>
+  </si>
+  <si>
+    <t>1) Age groups are defined as:
+   - Below 30 → age &lt; 30
+   - Above 30 → age &gt;= 30
+2) Most purchased product is based on count of orders
+3) Purchase count = COUNT(*) of records
+4) RANK() is used to get top product per age group
+5) If multiple products have same count, all are returned</t>
+  </si>
+  <si>
+    <t>1) Minimum is calculated using both:
+   - total transactions (COUNT)
+   - total amount (SUM)
+2) RANK() is used on both values to find minimum
+3) If multiple countries have same minimum, all are returned
+4) Only countries with orders are included (no empty countries)
+5) Total transactions = COUNT(order_id)
+   Total amount = SUM(amount)</t>
+  </si>
+  <si>
+    <t>1) Want to check if shipping should be linked at order level for better accuracy.
+2) Want to confirm how we should treat pending status? Should we consider only orders that are not yet delivered?
+3) Want to understand how to identify the latest status of an order? Should we use latest shipping_id or any date field if available?
+4) Since we are showing data at country level, should we include countries with no orders and show 0.00 amount, or skip them?</t>
+  </si>
+  <si>
+    <t>1) Help us understand how we should calculate quantity, since it is not available in the current data. Should we treat each order as quantity = 1, or is there any other table where we can get actual quantity per order ?
+2) Since quantity is not available, total amount per customer may not fully show the actual purchase (for example, one order may have multiple items but we are counting it as one). Could you please confirm if this approach is okay?
+3) For product details, should we group data by customer and product, or only at customer level? If we group only at customer level, how should we show item details — as a list of products or any other format? A sample output would really help us understand better.
+4) Since we are showing data at customer or customer-product level, should we include all customers even if they have no orders, or only customers who have placed orders?</t>
+  </si>
+  <si>
+    <t>1) Just wanted to confirm how we should define age groups. For example, if age is exactly 30, should it come under below 30 or above 30?
+2) How should we define "most purchased product"? Should it be based on number of orders (count) or based on total amount spent?
+3) If two or more products have the same purchase count in an age group, how should we handle it ? Should we show all products in one record like a list or should we populate in different records .
+4) Since quantity field is not available, we are using count of records as purchase count. Is there any other table where we can get actual quantity per order ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) If one country has minimum transactions and another country has minimum amount, which one should we return?
+2) If multiple countries have the same minimum value, should we show all of them or only one?
+3) If there are countries with no orders, should we include them with 0 values or skip them?
+4) Since quantity field is not available, we may get incorrect aggregate sum in total_amount field . Is there any other table where we can get actual quantity per order ?
+5) Would it be possible to share a sample output so we can better understand the expected result?
 </t>
   </si>
   <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Details</t>
-  </si>
-  <si>
-    <t>Objective</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Requirement 1 pending amount by country</t>
-  </si>
-  <si>
-    <t>Requirement 2 customer product summary</t>
-  </si>
-  <si>
-    <t>Requirement 3 top product by country</t>
-  </si>
-  <si>
-    <t>Requirement 4 top product by age group</t>
-  </si>
-  <si>
-    <t>Requirement 5 minimum transaction country</t>
-  </si>
-  <si>
-    <t>Approach</t>
-  </si>
-  <si>
-    <t>Data_Validation</t>
-  </si>
-  <si>
-    <t>Schema_Validation</t>
-  </si>
-  <si>
-    <t>Check grouping logic</t>
-  </si>
-  <si>
-    <t>Entry_Criteria</t>
-  </si>
-  <si>
-    <t>Gold tables are created</t>
-  </si>
-  <si>
-    <t>Exit_Criteria</t>
-  </si>
-  <si>
-    <t>Tools</t>
-  </si>
-  <si>
-    <t>Databricks</t>
-  </si>
-  <si>
-    <t>SQL</t>
-  </si>
-  <si>
-    <t>PySpark</t>
-  </si>
-  <si>
-    <t>Check data is correctly transformed from silver tables to gold tables</t>
-  </si>
-  <si>
-    <t>Check joins between tables</t>
-  </si>
-  <si>
-    <t>Check business logic</t>
-  </si>
-  <si>
-    <t>Validate using SQL queries</t>
-  </si>
-  <si>
-    <t>Check column names</t>
-  </si>
-  <si>
-    <t>Check data types</t>
-  </si>
-  <si>
-    <t>Check column mapping</t>
-  </si>
-  <si>
-    <t>Check row count match</t>
-  </si>
-  <si>
-    <t>Check sum min max avg values</t>
-  </si>
-  <si>
-    <t>Check no duplicate records</t>
-  </si>
-  <si>
-    <t>Check no null values</t>
-  </si>
-  <si>
-    <t>Transformation_Check</t>
-  </si>
-  <si>
-    <t>Check ranking logic</t>
-  </si>
-  <si>
-    <t>Business_Check</t>
-  </si>
-  <si>
-    <t>Validate all 5 requirements logic</t>
-  </si>
-  <si>
-    <t>Silver tables are ready</t>
-  </si>
-  <si>
-    <t>All tests completed</t>
-  </si>
-  <si>
-    <t>Results are correct</t>
-  </si>
-  <si>
-    <t>Customers ,Orders and Shipping to Gold tables</t>
-  </si>
-  <si>
-    <t>Check aggregations like sum,min,max,avg and count</t>
-  </si>
-  <si>
-    <t>Check filters like pending status and rank</t>
-  </si>
-  <si>
-    <t>Total_Test_Cases</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Bugs_Found</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>All validations passed successfully</t>
-  </si>
-  <si>
-    <t>REQ1</t>
-  </si>
-  <si>
-    <t>REQ2</t>
-  </si>
-  <si>
-    <t>REQ3</t>
-  </si>
-  <si>
-    <t>REQ4</t>
-  </si>
-  <si>
-    <t>REQ5</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Total_Requirements</t>
-  </si>
-  <si>
-    <t>Total_Test_Cases_Executed</t>
-  </si>
-  <si>
-    <t>Total_Test_Cases_Passed</t>
-  </si>
-  <si>
-    <t>Total_Test_Cases_Failed</t>
-  </si>
-  <si>
-    <t>Execution_Status</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Requirement_1_Test_Cases</t>
-  </si>
-  <si>
-    <t>Requirement_1_Passed</t>
-  </si>
-  <si>
-    <t>Requirement_1_Failed</t>
-  </si>
-  <si>
-    <t>Requirement_2_Test_Cases</t>
-  </si>
-  <si>
-    <t>Requirement_2_Passed</t>
-  </si>
-  <si>
-    <t>Requirement_2_Failed</t>
-  </si>
-  <si>
-    <t>Requirement_3_Test_Cases</t>
-  </si>
-  <si>
-    <t>Requirement_3_Passed</t>
-  </si>
-  <si>
-    <t>Requirement_3_Failed</t>
-  </si>
-  <si>
-    <t>Requirement_4_Test_Cases</t>
-  </si>
-  <si>
-    <t>Requirement_4_Passed</t>
-  </si>
-  <si>
-    <t>Requirement_4_Failed</t>
-  </si>
-  <si>
-    <t>Requirement_5_Test_Cases</t>
-  </si>
-  <si>
-    <t>Requirement_5_Passed</t>
-  </si>
-  <si>
-    <t>Requirement_5_Failed</t>
-  </si>
-  <si>
-    <t>Total_Defects</t>
-  </si>
-  <si>
-    <t>High_Severity_Defects</t>
-  </si>
-  <si>
-    <t>Medium_Severity_Defects</t>
-  </si>
-  <si>
-    <t>Low_Severity_Defects</t>
-  </si>
-  <si>
-    <t>All test cases passed successfully. No defects found. Any risks are documented as requirement gaps.</t>
-  </si>
-  <si>
-    <t>schema map silver to gold</t>
-  </si>
-  <si>
-    <t>metrics-summary</t>
-  </si>
-  <si>
-    <t>List of all 5 requirements to be built in gold layer</t>
-  </si>
-  <si>
-    <t>Simple plan to test data from silver to gold tables</t>
-  </si>
-  <si>
-    <t>List of questions and gaps found in requirements</t>
-  </si>
-  <si>
-    <t>Mapping of columns from silver tables to gold tables</t>
-  </si>
-  <si>
-    <t>All test cases for all 5 requirements</t>
-  </si>
-  <si>
-    <t>Summary of total test cases and results</t>
-  </si>
-  <si>
-    <t>Final output for Requirement 1</t>
-  </si>
-  <si>
-    <t>Final output for Requirement 2</t>
-  </si>
-  <si>
-    <t>Final output for Requirement 3</t>
-  </si>
-  <si>
-    <t>Final output for Requirement 4</t>
-  </si>
-  <si>
-    <t>Final output for Requirement 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheet Name </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Description</t>
-  </si>
-  <si>
-    <t>Sheet Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details of bugs found during testing </t>
-  </si>
-  <si>
-    <t>Test execution  of Requirement 1 test cases</t>
-  </si>
-  <si>
-    <t>Test execution  of Requirement 2 test cases</t>
-  </si>
-  <si>
-    <t>Test execution  of Requirement 3 test cases</t>
-  </si>
-  <si>
-    <t>Test execution  of Requirement 4 test cases</t>
-  </si>
-  <si>
-    <t>Test execution  of Requirement 5 test cases</t>
-  </si>
-  <si>
-    <t>Business Requirements'!A1</t>
-  </si>
-  <si>
-    <t>testplan - silver to gold'!A1</t>
-  </si>
-  <si>
-    <t>Gaps-Requirement gathering'!A1</t>
-  </si>
-  <si>
-    <t>schema map silver to gold'!A1</t>
-  </si>
-  <si>
-    <t>test cases'!A1</t>
-  </si>
-  <si>
-    <t>bug report'!A1</t>
-  </si>
-  <si>
-    <t>metrics-summary'!A1</t>
-  </si>
-  <si>
-    <t>REQ1_test_execution!A1</t>
-  </si>
-  <si>
-    <t>REQ1_test_final_results!A1</t>
-  </si>
-  <si>
-    <t>REQ2_test_execution!A1</t>
-  </si>
-  <si>
-    <t>REQ2_test_final_results!A1</t>
-  </si>
-  <si>
-    <t>REQ3_test_execution!A1</t>
-  </si>
-  <si>
-    <t>REQ3_test_final_results!A1</t>
-  </si>
-  <si>
-    <t>REQ4_test_execution!A1</t>
-  </si>
-  <si>
-    <t>REQ4_test_final_results!A1</t>
-  </si>
-  <si>
-    <t>REQ5_test_execution!A1</t>
-  </si>
-  <si>
-    <t>REQ5_test_final_results!A1</t>
-  </si>
-  <si>
-    <t>Business Requirements</t>
-  </si>
-  <si>
-    <t>testplan - silver to gold</t>
-  </si>
-  <si>
-    <t>Gaps-Requirement gathering</t>
-  </si>
-  <si>
-    <t>test cases</t>
-  </si>
-  <si>
-    <t>bug report</t>
+    <t>1) Shipping is linked using customer_id
+2) We are considering only records where status = 'Pending'
+3) We are not identifying latest status separately, we are directly using available status in shipping table
+4) Only countries with orders are included (countries with no orders are skipped)
+5) Total amount is calculated using SUM(order amount)</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1823,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1794,16 +1838,6 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1829,6 +1863,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6844,200 +6884,200 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>492</v>
+        <v>468</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>493</v>
+        <v>469</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>494</v>
+        <v>470</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>495</v>
+        <v>471</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>496</v>
+        <v>472</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>497</v>
+        <v>482</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>498</v>
+        <v>473</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>499</v>
+        <v>483</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>500</v>
+        <v>474</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>501</v>
+        <v>484</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>502</v>
+        <v>475</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>503</v>
+        <v>485</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>504</v>
+        <v>476</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>505</v>
+        <v>486</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>506</v>
+        <v>477</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>507</v>
+        <v>487</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>508</v>
+        <v>478</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -7693,111 +7733,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -8597,111 +8637,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -9352,111 +9392,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -10078,111 +10118,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -10671,7 +10711,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>193</v>
@@ -10679,7 +10719,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>192</v>
@@ -10687,7 +10727,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>191</v>
@@ -10695,7 +10735,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>190</v>
@@ -10703,7 +10743,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>189</v>
@@ -10726,242 +10766,242 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>392</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -10975,77 +11015,93 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="2" max="2" width="64.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.6640625" customWidth="1"/>
     <col min="3" max="3" width="70.44140625" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="14"/>
+    <col min="4" max="4" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="12" t="s">
         <v>383</v>
       </c>
+      <c r="D1" s="12" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>385</v>
-      </c>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>388</v>
+      <c r="C6" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -11577,16 +11633,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -12082,16 +12138,16 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
@@ -12819,16 +12875,16 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
@@ -13353,16 +13409,16 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="22"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
+      <c r="A78" s="22"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
@@ -13858,16 +13914,16 @@
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="12" t="s">
+      <c r="A102" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
+      <c r="B102" s="22"/>
+      <c r="C102" s="22"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="12"/>
-      <c r="B103" s="12"/>
-      <c r="C103" s="12"/>
+      <c r="A103" s="22"/>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
@@ -14504,141 +14560,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>430</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="G1" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="D1" s="21" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="18">
+        <v>16</v>
+      </c>
+      <c r="C2" s="18">
+        <v>16</v>
+      </c>
+      <c r="D2" s="18">
+        <v>0</v>
+      </c>
+      <c r="E2" s="18">
+        <v>0</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="G2" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="F1" s="21" t="s">
-        <v>434</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="22">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="18">
+        <v>24</v>
+      </c>
+      <c r="C3" s="18">
+        <v>24</v>
+      </c>
+      <c r="D3" s="18">
+        <v>0</v>
+      </c>
+      <c r="E3" s="18">
+        <v>0</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="18">
+        <v>17</v>
+      </c>
+      <c r="C4" s="18">
+        <v>17</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0</v>
+      </c>
+      <c r="E4" s="18">
+        <v>0</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="18">
         <v>16</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C5" s="18">
         <v>16</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D5" s="18">
         <v>0</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E5" s="18">
         <v>0</v>
       </c>
-      <c r="F2" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="22">
-        <v>24</v>
-      </c>
-      <c r="C3" s="22">
-        <v>24</v>
-      </c>
-      <c r="D3" s="22">
+      <c r="F5" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="18">
+        <v>20</v>
+      </c>
+      <c r="C6" s="18">
+        <v>20</v>
+      </c>
+      <c r="D6" s="18">
         <v>0</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E6" s="18">
         <v>0</v>
       </c>
-      <c r="F3" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="22">
-        <v>17</v>
-      </c>
-      <c r="C4" s="22">
-        <v>17</v>
-      </c>
-      <c r="D4" s="22">
-        <v>0</v>
-      </c>
-      <c r="E4" s="22">
-        <v>0</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="22">
-        <v>16</v>
-      </c>
-      <c r="C5" s="22">
-        <v>16</v>
-      </c>
-      <c r="D5" s="22">
-        <v>0</v>
-      </c>
-      <c r="E5" s="22">
-        <v>0</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="22">
-        <v>20</v>
-      </c>
-      <c r="C6" s="22">
-        <v>20</v>
-      </c>
-      <c r="D6" s="22">
-        <v>0</v>
-      </c>
-      <c r="E6" s="22">
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>436</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>437</v>
+      <c r="F6" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -14656,219 +14712,219 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="B2" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="B3" s="16">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="B4" s="16">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="B5" s="16">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>443</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="B6" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
         <v>444</v>
       </c>
-      <c r="B2" s="20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>430</v>
-      </c>
-      <c r="B3" s="20">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>445</v>
       </c>
-      <c r="B4" s="20">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="B5" s="20">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="B8" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B9" s="16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="B10" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="B7" s="20" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="B11" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B12" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B13" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="B14" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="B16" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="B17" s="16">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
-        <v>451</v>
-      </c>
-      <c r="B9" s="20">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="B18" s="16">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="B10" s="20">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="B19" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
-        <v>453</v>
-      </c>
-      <c r="B11" s="20">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
-        <v>454</v>
-      </c>
-      <c r="B12" s="20">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
-        <v>455</v>
-      </c>
-      <c r="B13" s="20">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B20" s="16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="B21" s="16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="B22" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
-        <v>456</v>
-      </c>
-      <c r="B14" s="20">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
-        <v>457</v>
-      </c>
-      <c r="B15" s="20">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="B16" s="20">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="B23" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="B17" s="20">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
-        <v>460</v>
-      </c>
-      <c r="B18" s="20">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="B19" s="20">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="B24" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="B20" s="20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="B21" s="20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+      <c r="B25" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B26" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>465</v>
-      </c>
-      <c r="B23" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
-        <v>466</v>
-      </c>
-      <c r="B24" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="B25" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="B26" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -15086,111 +15142,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+      <c r="O69" s="21"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="21"/>
+      <c r="L70" s="21"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="21"/>
+      <c r="L74" s="21"/>
+      <c r="M74" s="21"/>
+      <c r="N74" s="21"/>
+      <c r="O74" s="21"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">

--- a/silver_to_gold_validation.xlsx
+++ b/silver_to_gold_validation.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uthej\Downloads\PEI_assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE55B3A6-26F0-4753-9811-5A5F4EE24BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FA809B-8C68-42A5-ABC3-D7C849500C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BC5507A9-D27E-444C-93EA-C153FA16561C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{BC5507A9-D27E-444C-93EA-C153FA16561C}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet index - content" sheetId="22" r:id="rId1"/>
     <sheet name="Business Requirements" sheetId="8" r:id="rId2"/>
-    <sheet name="testplan - silver to gold" sheetId="19" r:id="rId3"/>
-    <sheet name="Gaps-Requirement gathering" sheetId="18" r:id="rId4"/>
-    <sheet name="schema map silver to gold" sheetId="1" r:id="rId5"/>
+    <sheet name="schema map silver to gold" sheetId="1" r:id="rId3"/>
+    <sheet name="testplan - silver to gold" sheetId="19" r:id="rId4"/>
+    <sheet name="Gaps-Requirement gathering" sheetId="18" r:id="rId5"/>
     <sheet name="test cases" sheetId="3" r:id="rId6"/>
     <sheet name="bug report" sheetId="20" r:id="rId7"/>
     <sheet name="metrics-summary" sheetId="21" r:id="rId8"/>
@@ -1678,12 +1678,6 @@
    Total amount = SUM(amount)</t>
   </si>
   <si>
-    <t>1) Want to check if shipping should be linked at order level for better accuracy.
-2) Want to confirm how we should treat pending status? Should we consider only orders that are not yet delivered?
-3) Want to understand how to identify the latest status of an order? Should we use latest shipping_id or any date field if available?
-4) Since we are showing data at country level, should we include countries with no orders and show 0.00 amount, or skip them?</t>
-  </si>
-  <si>
     <t>1) Help us understand how we should calculate quantity, since it is not available in the current data. Should we treat each order as quantity = 1, or is there any other table where we can get actual quantity per order ?
 2) Since quantity is not available, total amount per customer may not fully show the actual purchase (for example, one order may have multiple items but we are counting it as one). Could you please confirm if this approach is okay?
 3) For product details, should we group data by customer and product, or only at customer level? If we group only at customer level, how should we show item details — as a list of products or any other format? A sample output would really help us understand better.
@@ -1708,7 +1702,15 @@
 2) We are considering only records where status = 'Pending'
 3) We are not identifying latest status separately, we are directly using available status in shipping table
 4) Only countries with orders are included (countries with no orders are skipped)
-5) Total amount is calculated using SUM(order amount)</t>
+5) Total amount is calculated using SUM(order amount)
+6) One order=One quantity</t>
+  </si>
+  <si>
+    <t>1) Want to check if shipping should be linked at order level for better accuracy.
+2) Want to confirm how we should treat pending status? Should we consider only orders that are not yet delivered?
+3) Want to understand how to identify the latest status of an order? Should we use latest shipping_id or any date field if available?
+4) Since we are showing data at country level, should we include countries with no orders and show 0.00 amount, or skip them?
+5) Quantity field missing in orders table , is there any other table where we can get actual quantity per order ?</t>
   </si>
 </sst>
 </file>
@@ -1863,10 +1865,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2095,13 +2097,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>29688</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>511007</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>152619</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>4177</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2124,8 +2126,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1592580" y="731520"/>
-          <a:ext cx="5387807" cy="2530059"/>
+          <a:off x="1593273" y="742207"/>
+          <a:ext cx="5419474" cy="2468308"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7733,111 +7735,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -8637,111 +8639,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -9392,111 +9394,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -10118,111 +10120,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
@@ -10756,6 +10758,510 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1008E9C9-909F-4323-A504-2DBF27662DB8}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E4BCD3-1989-4625-97D6-E02D408A69BE}">
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11009,7 +11515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2839FD62-2A6C-4A53-8548-2FB7611B952C}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11034,7 +11540,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>434</v>
       </c>
@@ -11042,10 +11548,10 @@
         <v>193</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
@@ -11056,7 +11562,7 @@
         <v>192</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>511</v>
@@ -11084,7 +11590,7 @@
         <v>190</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>513</v>
@@ -11098,514 +11604,10 @@
         <v>189</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>514</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1008E9C9-909F-4323-A504-2DBF27662DB8}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -11622,7 +11624,7 @@
     <col min="1" max="1" width="16.77734375" style="1" customWidth="1"/>
     <col min="2" max="3" width="20.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="62.88671875" style="1" customWidth="1"/>
     <col min="6" max="6" width="27.88671875" style="1" customWidth="1"/>
     <col min="7" max="7" width="24.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="106" style="1" customWidth="1"/>
@@ -11633,16 +11635,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -11686,7 +11688,7 @@
       <c r="D6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>175</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -11840,7 +11842,7 @@
       <c r="G11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>105</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -11985,7 +11987,7 @@
       <c r="G16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>173</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -12014,7 +12016,7 @@
       <c r="G17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="4" t="s">
         <v>172</v>
       </c>
       <c r="I17" s="3" t="s">
@@ -12043,7 +12045,7 @@
       <c r="G18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="4" t="s">
         <v>171</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -12138,16 +12140,16 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
@@ -12875,16 +12877,16 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="22"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="22"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
@@ -13409,16 +13411,16 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="22" t="s">
+      <c r="A77" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B77" s="22"/>
-      <c r="C77" s="22"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="21"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="22"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="22"/>
+      <c r="A78" s="21"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
@@ -13914,16 +13916,16 @@
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="22" t="s">
+      <c r="A102" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B102" s="22"/>
-      <c r="C102" s="22"/>
+      <c r="B102" s="21"/>
+      <c r="C102" s="21"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="22"/>
-      <c r="B103" s="22"/>
-      <c r="C103" s="22"/>
+      <c r="A103" s="21"/>
+      <c r="B103" s="21"/>
+      <c r="C103" s="21"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
@@ -15142,111 +15144,111 @@
       </c>
     </row>
     <row r="68" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C68" s="21" t="s">
+      <c r="C68" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="22"/>
+      <c r="J68" s="22"/>
+      <c r="K68" s="22"/>
+      <c r="L68" s="22"/>
+      <c r="M68" s="22"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="22"/>
     </row>
     <row r="69" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="21"/>
-      <c r="N69" s="21"/>
-      <c r="O69" s="21"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="22"/>
+      <c r="J69" s="22"/>
+      <c r="K69" s="22"/>
+      <c r="L69" s="22"/>
+      <c r="M69" s="22"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="22"/>
+      <c r="K70" s="22"/>
+      <c r="L70" s="22"/>
+      <c r="M70" s="22"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="71" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="22"/>
+      <c r="K71" s="22"/>
+      <c r="L71" s="22"/>
+      <c r="M71" s="22"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="22"/>
     </row>
     <row r="72" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="22"/>
+      <c r="L72" s="22"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="22"/>
     </row>
     <row r="73" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" spans="3:15" x14ac:dyDescent="0.3">
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
